--- a/Files/Documents/Dataset.xlsx
+++ b/Files/Documents/Dataset.xlsx
@@ -1,42 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="555" windowWidth="14055" windowHeight="4050"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,23 +49,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -348,18 +433,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="100" customWidth="1"/>
-    <col min="5" max="6" width="20" customWidth="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="50" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Lyrics</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>LRC Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Never Gonna Give You Up</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Rick Astley</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[00:18.92] We're no strangers to love [00:22.59] You know the rules and so do I (do I) [00:26.93] A full commitment's what I'm thinking of [00:31.35] You wouldn't get this from any other guy [00:35.14] I just wanna tell you how I'm feeling [00:40.28] Gotta make you understand [00:42.83] Never gonna give you up [00:45.22] Never gonna let you down [00:47.14] Never gonna run around and desert you [00:51.40] Never gonna make you cry [00:53.88] Never gonna say goodbye [00:55.67] Never gonna tell a lie and hurt you [01:00.52] We've known each other for so long [01:05.04] Your heart's been aching, but you're too shy to say it (say it) [01:09.42] Inside, we both know what's been going on (going on) [01:13.11] We know the game and we're gonna play it [01:17.29] And if you ask me how I'm feeling [01:22.51] Don't tell me you're too blind to see [01:25.33] Never gonna give you up [01:27.47] Never gonna let you down [01:29.65] Never gonna run around and desert you [01:33.42] Never gonna make you cry [01:35.82] Never gonna say goodbye [01:37.78] Never gonna tell a lie and hurt you [01:41.99] Never gonna give you up [01:44.10] Never gonna let you down [01:46.43] Never gonna run around and desert you [01:50.26] Never gonna make you cry [01:52.56] Never gonna say goodbye [01:54.79] Never gonna tell a lie and hurt you [01:59.22] (Ooh, give you up) [02:02.98] (Ooh, give you up) [02:07.08] (Ooh) Never gonna give, never gonna give (give you up) [02:11.26] (Ooh) Never gonna give, never gonna give (give you up) [02:16.13] We've known each other for so long [02:20.53] Your heart's been aching, but you're too shy to say it (to say it) [02:24.65] Inside, we both know what's been going on (going on) [02:28.87] We know the game and we're gonna play it [02:32.55] I just wanna tell you how I'm feeling [02:37.79] Gotta make you understand [02:40.88] Never gonna give you up [02:42.94] Never gonna let you down [02:45.16] Never gonna run around and desert you [02:49.00] Never gonna make you cry [02:51.17] Never gonna say goodbye [02:53.78] Never gonna tell a lie and hurt you [02:57.61] Never gonna give you up [02:59.47] Never gonna let you down [03:02.00] Never gonna run around and desert you [03:05.95] Never gonna make you cry [03:08.34] Never gonna say goodbye [03:10.45] Never gonna tell a lie and hurt you [03:14.37] Never gonna give you up [03:16.37] Never gonna let you down [03:18.84] Never gonna run around and desert you [03:23.07] Never gonna make you cry [03:25.17] Never gonna say goodbye [03:27.38] Never gonna tell a lie and hurt you [03:30.57] </t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Synced</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
